--- a/metalman-auto-engineer/backend/outputs/Fitment_Checksheet_92187158.xlsx
+++ b/metalman-auto-engineer/backend/outputs/Fitment_Checksheet_92187158.xlsx
@@ -1264,7 +1264,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1289,7 +1289,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1314,7 +1314,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1339,7 +1339,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1364,7 +1364,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1389,7 +1389,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1414,7 +1414,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1439,7 +1439,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1464,7 +1464,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1489,7 +1489,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -1514,7 +1514,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -1539,7 +1539,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -1564,7 +1564,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -1589,7 +1589,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -1614,7 +1614,7 @@
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -1639,7 +1639,7 @@
       <row>24</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="857250"/>
+    <ext cx="1381125" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -1933,7 +1933,7 @@
     <col width="11.26953125" customWidth="1" style="3" min="1" max="1"/>
     <col width="43" customWidth="1" style="1" min="2" max="2"/>
     <col width="19.26953125" customWidth="1" style="1" min="3" max="3"/>
-    <col width="35.26953125" customWidth="1" style="3" min="4" max="4"/>
+    <col width="28" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" customWidth="1" style="8" min="5" max="5"/>
     <col width="19.54296875" customWidth="1" style="2" min="6" max="10"/>
     <col width="18.453125" customWidth="1" style="2" min="11" max="11"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J4" s="79" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>01-06-2026</t>
         </is>
       </c>
       <c r="K4" s="80" t="n"/>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="85" customHeight="1">
+    <row r="9" ht="95" customHeight="1">
       <c r="A9" s="25" t="n">
         <v>1</v>
       </c>
@@ -2190,7 +2190,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="17" t="inlineStr"/>
     </row>
-    <row r="10" ht="85" customHeight="1">
+    <row r="10" ht="95" customHeight="1">
       <c r="A10" s="25" t="n">
         <v>2</v>
       </c>
@@ -2215,7 +2215,7 @@
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="17" t="inlineStr"/>
     </row>
-    <row r="11" ht="85" customHeight="1">
+    <row r="11" ht="95" customHeight="1">
       <c r="A11" s="25" t="n">
         <v>3</v>
       </c>
@@ -2240,7 +2240,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="17" t="inlineStr"/>
     </row>
-    <row r="12" ht="85" customHeight="1">
+    <row r="12" ht="95" customHeight="1">
       <c r="A12" s="25" t="n">
         <v>4</v>
       </c>
@@ -2265,7 +2265,7 @@
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="17" t="inlineStr"/>
     </row>
-    <row r="13" ht="85" customHeight="1">
+    <row r="13" ht="95" customHeight="1">
       <c r="A13" s="25" t="n">
         <v>5</v>
       </c>
@@ -2290,7 +2290,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="17" t="inlineStr"/>
     </row>
-    <row r="14" ht="85" customHeight="1">
+    <row r="14" ht="95" customHeight="1">
       <c r="A14" s="25" t="n">
         <v>6</v>
       </c>
@@ -2315,7 +2315,7 @@
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="17" t="inlineStr"/>
     </row>
-    <row r="15" ht="85" customHeight="1">
+    <row r="15" ht="95" customHeight="1">
       <c r="A15" s="25" t="n">
         <v>7</v>
       </c>
@@ -2340,7 +2340,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="17" t="inlineStr"/>
     </row>
-    <row r="16" ht="85" customHeight="1">
+    <row r="16" ht="95" customHeight="1">
       <c r="A16" s="25" t="n">
         <v>8</v>
       </c>
@@ -2365,7 +2365,7 @@
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="17" t="inlineStr"/>
     </row>
-    <row r="17" ht="85" customHeight="1">
+    <row r="17" ht="95" customHeight="1">
       <c r="A17" s="25" t="n">
         <v>9</v>
       </c>
@@ -2390,7 +2390,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="17" t="inlineStr"/>
     </row>
-    <row r="18" ht="85" customHeight="1">
+    <row r="18" ht="95" customHeight="1">
       <c r="A18" s="25" t="n">
         <v>10</v>
       </c>
@@ -2415,7 +2415,7 @@
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="17" t="inlineStr"/>
     </row>
-    <row r="19" ht="85" customHeight="1">
+    <row r="19" ht="95" customHeight="1">
       <c r="A19" s="25" t="n">
         <v>11</v>
       </c>
@@ -2440,7 +2440,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="17" t="inlineStr"/>
     </row>
-    <row r="20" ht="85" customHeight="1">
+    <row r="20" ht="95" customHeight="1">
       <c r="A20" s="25" t="n">
         <v>12</v>
       </c>
@@ -2465,7 +2465,7 @@
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="17" t="inlineStr"/>
     </row>
-    <row r="21" ht="85" customHeight="1">
+    <row r="21" ht="95" customHeight="1">
       <c r="A21" s="25" t="n">
         <v>13</v>
       </c>
@@ -2515,7 +2515,7 @@
       <c r="J22" s="4" t="inlineStr"/>
       <c r="K22" s="17" t="inlineStr"/>
     </row>
-    <row r="23" ht="85" customHeight="1">
+    <row r="23" ht="95" customHeight="1">
       <c r="A23" s="25" t="n">
         <v>16</v>
       </c>
@@ -2540,7 +2540,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="17" t="inlineStr"/>
     </row>
-    <row r="24" ht="85" customHeight="1">
+    <row r="24" ht="95" customHeight="1">
       <c r="A24" s="25" t="n">
         <v>17</v>
       </c>
@@ -2565,7 +2565,7 @@
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="17" t="inlineStr"/>
     </row>
-    <row r="25" ht="85" customHeight="1">
+    <row r="25" ht="95" customHeight="1">
       <c r="A25" s="25" t="n">
         <v>18</v>
       </c>

--- a/metalman-auto-engineer/backend/outputs/Fitment_Checksheet_92187158.xlsx
+++ b/metalman-auto-engineer/backend/outputs/Fitment_Checksheet_92187158.xlsx
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J4" s="79" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="K4" s="80" t="n"/>
